--- a/20260330_vcp_scan_score4plus_filtered.xlsx
+++ b/20260330_vcp_scan_score4plus_filtered.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,7 +1009,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SIRI</t>
+          <t>WTTR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1023,26 +1023,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22.84000015258789</v>
+        <v>15.60999965667725</v>
       </c>
       <c r="E11" t="n">
-        <v>23.10000038146973</v>
+        <v>15.72999954223633</v>
       </c>
       <c r="F11" t="n">
-        <v>22.76000022888184</v>
+        <v>15.48499965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>2573100</v>
+        <v>1312900</v>
       </c>
       <c r="H11" t="n">
-        <v>58769604.3926239</v>
+        <v>20494368.54925156</v>
       </c>
       <c r="I11" t="n">
-        <v>22.6299991607666</v>
+        <v>14.02999973297119</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.8|4.15|2.83</t>
+          <t>11.66|2.82|1.14</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WTTR</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1080,50 +1080,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.60999965667725</v>
+        <v>248.8000030517578</v>
       </c>
       <c r="E12" t="n">
-        <v>15.72999954223633</v>
+        <v>255.4900054931641</v>
       </c>
       <c r="F12" t="n">
-        <v>15.48499965667725</v>
+        <v>248.0700073242188</v>
       </c>
       <c r="G12" t="n">
-        <v>1312900</v>
+        <v>47842500</v>
       </c>
       <c r="H12" t="n">
-        <v>20494368.54925156</v>
+        <v>11903214146.00372</v>
       </c>
       <c r="I12" t="n">
-        <v>14.02999973297119</v>
+        <v>260.8299865722656</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11.66|2.82|1.14</t>
+          <t>7.95|6.12|4.92</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
         <v>260</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>perfect vcp setup</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BAP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1137,26 +1133,26 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>248.8000030517578</v>
+        <v>322.4299926757812</v>
       </c>
       <c r="E13" t="n">
-        <v>255.4900054931641</v>
+        <v>329.8900146484375</v>
       </c>
       <c r="F13" t="n">
-        <v>248.0700073242188</v>
+        <v>319.7699890136719</v>
       </c>
       <c r="G13" t="n">
-        <v>47842500</v>
+        <v>384300</v>
       </c>
       <c r="H13" t="n">
-        <v>11903214146.00372</v>
+        <v>123909846.1853027</v>
       </c>
       <c r="I13" t="n">
-        <v>260.8299865722656</v>
+        <v>334.5799865722656</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.95|6.12|4.92</t>
+          <t>12.11|8.52|3.87</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1176,7 +1172,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1190,26 +1186,26 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>322.4299926757812</v>
+        <v>219.1399993896484</v>
       </c>
       <c r="E14" t="n">
-        <v>329.8900146484375</v>
+        <v>220.3899993896484</v>
       </c>
       <c r="F14" t="n">
-        <v>319.7699890136719</v>
+        <v>214.4299926757812</v>
       </c>
       <c r="G14" t="n">
-        <v>384300</v>
+        <v>1291600</v>
       </c>
       <c r="H14" t="n">
-        <v>123909846.1853027</v>
+        <v>283041223.2116699</v>
       </c>
       <c r="I14" t="n">
-        <v>334.5799865722656</v>
+        <v>222.520004272461</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12.11|8.52|3.87</t>
+          <t>9.04|8.33|6.08</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1229,7 +1225,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>CKX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1243,26 +1239,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>219.1399993896484</v>
+        <v>10.98999977111816</v>
       </c>
       <c r="E15" t="n">
-        <v>220.3899993896484</v>
+        <v>10.98999977111816</v>
       </c>
       <c r="F15" t="n">
-        <v>214.4299926757812</v>
+        <v>10.98999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>1291600</v>
+        <v>300</v>
       </c>
       <c r="H15" t="n">
-        <v>283041223.2116699</v>
+        <v>3296.999931335449</v>
       </c>
       <c r="I15" t="n">
-        <v>222.520004272461</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.04|8.33|6.08</t>
+          <t>13.84|6.33|5.88</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1282,7 +1278,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CKX</t>
+          <t>CRTO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1296,26 +1292,26 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.98999977111816</v>
+        <v>17.18000030517578</v>
       </c>
       <c r="E16" t="n">
-        <v>10.98999977111816</v>
+        <v>17.44499969482422</v>
       </c>
       <c r="F16" t="n">
-        <v>10.98999977111816</v>
+        <v>16.98500061035156</v>
       </c>
       <c r="G16" t="n">
-        <v>300</v>
+        <v>218800</v>
       </c>
       <c r="H16" t="n">
-        <v>3296.999931335449</v>
+        <v>3758984.066772461</v>
       </c>
       <c r="I16" t="n">
-        <v>11.05000019073486</v>
+        <v>18.02000045776367</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.84|6.33|5.88</t>
+          <t>12.52|10.23|5.66</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1335,7 +1331,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CRTO</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1349,26 +1345,26 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.18000030517578</v>
+        <v>114.6100006103516</v>
       </c>
       <c r="E17" t="n">
-        <v>17.44499969482422</v>
+        <v>116.3099975585938</v>
       </c>
       <c r="F17" t="n">
-        <v>16.98500061035156</v>
+        <v>113</v>
       </c>
       <c r="G17" t="n">
-        <v>218800</v>
+        <v>296800</v>
       </c>
       <c r="H17" t="n">
-        <v>3758984.066772461</v>
+        <v>34016248.18115234</v>
       </c>
       <c r="I17" t="n">
-        <v>18.02000045776367</v>
+        <v>102.6999969482422</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12.52|10.23|5.66</t>
+          <t>11.06|3.53|1.56</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -1382,13 +1378,13 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1402,26 +1398,26 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>114.6100006103516</v>
+        <v>41.52999877929688</v>
       </c>
       <c r="E18" t="n">
-        <v>116.3099975585938</v>
+        <v>41.56999969482422</v>
       </c>
       <c r="F18" t="n">
-        <v>113</v>
+        <v>40.95999908447266</v>
       </c>
       <c r="G18" t="n">
-        <v>296800</v>
+        <v>8502700</v>
       </c>
       <c r="H18" t="n">
-        <v>34016248.18115234</v>
+        <v>353117120.6207275</v>
       </c>
       <c r="I18" t="n">
-        <v>102.6999969482422</v>
+        <v>32.06999969482422</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.06|3.53|1.56</t>
+          <t>3.86|3.57|3.39</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -1435,13 +1431,13 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1455,26 +1451,26 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>41.52999877929688</v>
+        <v>56.22000122070312</v>
       </c>
       <c r="E19" t="n">
-        <v>41.56999969482422</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>40.95999908447266</v>
+        <v>55.27999877929688</v>
       </c>
       <c r="G19" t="n">
-        <v>8502700</v>
+        <v>9700</v>
       </c>
       <c r="H19" t="n">
-        <v>353117120.6207275</v>
+        <v>545334.0118408203</v>
       </c>
       <c r="I19" t="n">
-        <v>32.06999969482422</v>
+        <v>55.97999954223633</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.86|3.57|3.39</t>
+          <t>7.72|7.05|4.41</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -1488,13 +1484,13 @@
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1508,26 +1504,26 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>56.22000122070312</v>
+        <v>64.80000305175781</v>
       </c>
       <c r="E20" t="n">
-        <v>57</v>
+        <v>65.69999694824219</v>
       </c>
       <c r="F20" t="n">
-        <v>55.27999877929688</v>
+        <v>63.83000183105469</v>
       </c>
       <c r="G20" t="n">
-        <v>9700</v>
+        <v>2501400</v>
       </c>
       <c r="H20" t="n">
-        <v>545334.0118408203</v>
+        <v>162090727.633667</v>
       </c>
       <c r="I20" t="n">
-        <v>55.97999954223633</v>
+        <v>65.81999969482422</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.72|7.05|4.41</t>
+          <t>11.23|5.25|4.25</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -1547,7 +1543,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>FSEA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1561,26 +1557,26 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64.80000305175781</v>
+        <v>12.72000026702881</v>
       </c>
       <c r="E21" t="n">
-        <v>65.69999694824219</v>
+        <v>12.85999965667725</v>
       </c>
       <c r="F21" t="n">
-        <v>63.83000183105469</v>
+        <v>12.71000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>2501400</v>
+        <v>1500</v>
       </c>
       <c r="H21" t="n">
-        <v>162090727.633667</v>
+        <v>19080.00040054321</v>
       </c>
       <c r="I21" t="n">
-        <v>65.81999969482422</v>
+        <v>13.05000019073486</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.23|5.25|4.25</t>
+          <t>3.69|2.39|2.15</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -1594,13 +1590,13 @@
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FSEA</t>
+          <t>HQL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1614,26 +1610,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.72000026702881</v>
+        <v>16.04999923706055</v>
       </c>
       <c r="E22" t="n">
-        <v>12.85999965667725</v>
+        <v>16.52000045776367</v>
       </c>
       <c r="F22" t="n">
-        <v>12.71000003814697</v>
+        <v>16.01000022888184</v>
       </c>
       <c r="G22" t="n">
-        <v>1500</v>
+        <v>92000</v>
       </c>
       <c r="H22" t="n">
-        <v>19080.00040054321</v>
+        <v>1476599.92980957</v>
       </c>
       <c r="I22" t="n">
-        <v>13.05000019073486</v>
+        <v>16.6200008392334</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.69|2.39|2.15</t>
+          <t>6.3|2.96|2.65</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -1653,7 +1649,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HQL</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1667,26 +1663,26 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.04999923706055</v>
+        <v>24.68000030517578</v>
       </c>
       <c r="E23" t="n">
-        <v>16.52000045776367</v>
+        <v>25.04999923706055</v>
       </c>
       <c r="F23" t="n">
-        <v>16.01000022888184</v>
+        <v>24.04999923706055</v>
       </c>
       <c r="G23" t="n">
-        <v>92000</v>
+        <v>745500</v>
       </c>
       <c r="H23" t="n">
-        <v>1476599.92980957</v>
+        <v>18398940.22750854</v>
       </c>
       <c r="I23" t="n">
-        <v>16.6200008392334</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6.3|2.96|2.65</t>
+          <t>39.44|23.77|12.84</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -1706,7 +1702,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>KRYS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1720,26 +1716,26 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.68000030517578</v>
+        <v>245.3899993896484</v>
       </c>
       <c r="E24" t="n">
-        <v>25.04999923706055</v>
+        <v>249.6000061035156</v>
       </c>
       <c r="F24" t="n">
-        <v>24.04999923706055</v>
+        <v>242.2599945068359</v>
       </c>
       <c r="G24" t="n">
-        <v>745500</v>
+        <v>289700</v>
       </c>
       <c r="H24" t="n">
-        <v>18398940.22750854</v>
+        <v>71089482.82318115</v>
       </c>
       <c r="I24" t="n">
-        <v>25.68000030517578</v>
+        <v>258</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>39.44|23.77|12.84</t>
+          <t>9.05|6.35|5.29</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -1759,7 +1755,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KRYS</t>
+          <t>LOCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1773,26 +1769,26 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>245.3899993896484</v>
+        <v>13.8100004196167</v>
       </c>
       <c r="E25" t="n">
-        <v>249.6000061035156</v>
+        <v>14.02000045776367</v>
       </c>
       <c r="F25" t="n">
-        <v>242.2599945068359</v>
+        <v>13.32999992370606</v>
       </c>
       <c r="G25" t="n">
-        <v>289700</v>
+        <v>522400</v>
       </c>
       <c r="H25" t="n">
-        <v>71089482.82318115</v>
+        <v>7214344.219207764</v>
       </c>
       <c r="I25" t="n">
-        <v>258</v>
+        <v>14.32999992370606</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>9.05|6.35|5.29</t>
+          <t>10.75|5.12|1.26</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -1812,7 +1808,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1826,26 +1822,26 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.8100004196167</v>
+        <v>94.87999725341795</v>
       </c>
       <c r="E26" t="n">
-        <v>14.02000045776367</v>
+        <v>99.62999725341795</v>
       </c>
       <c r="F26" t="n">
-        <v>13.32999992370606</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="G26" t="n">
-        <v>522400</v>
+        <v>16478700</v>
       </c>
       <c r="H26" t="n">
-        <v>7214344.219207764</v>
+        <v>1563499010.739899</v>
       </c>
       <c r="I26" t="n">
-        <v>14.32999992370606</v>
+        <v>91.58000183105467</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>10.75|5.12|1.26</t>
+          <t>7.36|6.03|4.32</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -1865,7 +1861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1879,26 +1875,26 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>94.87999725341795</v>
+        <v>128.3200073242188</v>
       </c>
       <c r="E27" t="n">
-        <v>99.62999725341795</v>
+        <v>132.9499969482422</v>
       </c>
       <c r="F27" t="n">
-        <v>93.40000152587891</v>
+        <v>128.0200042724609</v>
       </c>
       <c r="G27" t="n">
-        <v>16478700</v>
+        <v>761300</v>
       </c>
       <c r="H27" t="n">
-        <v>1563499010.739899</v>
+        <v>97690021.57592772</v>
       </c>
       <c r="I27" t="n">
-        <v>91.58000183105467</v>
+        <v>130.7100067138672</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>7.36|6.03|4.32</t>
+          <t>12.82|3.98|2.8</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -1912,13 +1908,13 @@
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>OIS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1932,26 +1928,26 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>128.3200073242188</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="E28" t="n">
-        <v>132.9499969482422</v>
+        <v>12.47999954223633</v>
       </c>
       <c r="F28" t="n">
-        <v>128.0200042724609</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>761300</v>
+        <v>932600</v>
       </c>
       <c r="H28" t="n">
-        <v>97690021.57592772</v>
+        <v>11377719.82212067</v>
       </c>
       <c r="I28" t="n">
-        <v>130.7100067138672</v>
+        <v>12.26000022888184</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>12.82|3.98|2.8</t>
+          <t>15.01|7.76|3.02</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -1965,13 +1961,13 @@
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OIS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1985,26 +1981,26 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.19999980926514</v>
+        <v>21.64999961853027</v>
       </c>
       <c r="E29" t="n">
-        <v>12.47999954223633</v>
+        <v>21.79999923706055</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>21.42000007629395</v>
       </c>
       <c r="G29" t="n">
-        <v>932600</v>
+        <v>12497000</v>
       </c>
       <c r="H29" t="n">
-        <v>11377719.82212067</v>
+        <v>270560045.2327728</v>
       </c>
       <c r="I29" t="n">
-        <v>12.26000022888184</v>
+        <v>19.18900108337402</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>15.01|7.76|3.02</t>
+          <t>6.25|2.66|1.95</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -2024,7 +2020,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>REAX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2038,26 +2034,26 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>21.64999961853027</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="E30" t="n">
-        <v>21.79999923706055</v>
+        <v>2.424999952316284</v>
       </c>
       <c r="F30" t="n">
-        <v>21.42000007629395</v>
+        <v>2.365000009536743</v>
       </c>
       <c r="G30" t="n">
-        <v>12497000</v>
+        <v>881200</v>
       </c>
       <c r="H30" t="n">
-        <v>270560045.2327728</v>
+        <v>2114880.084037781</v>
       </c>
       <c r="I30" t="n">
-        <v>19.18900108337402</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6.25|2.66|1.95</t>
+          <t>22.36|15.16|5.22</t>
         </is>
       </c>
       <c r="K30" t="b">
@@ -2071,13 +2067,13 @@
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REAX</t>
+          <t>RNWWW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2091,26 +2087,26 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.400000095367432</v>
+        <v>0.0080000003799796</v>
       </c>
       <c r="E31" t="n">
-        <v>2.424999952316284</v>
+        <v>0.0080000003799796</v>
       </c>
       <c r="F31" t="n">
-        <v>2.365000009536743</v>
+        <v>0.003000000026077</v>
       </c>
       <c r="G31" t="n">
-        <v>881200</v>
+        <v>82200</v>
       </c>
       <c r="H31" t="n">
-        <v>2114880.084037781</v>
+        <v>657.600031234324</v>
       </c>
       <c r="I31" t="n">
-        <v>2.440000057220459</v>
+        <v>0.006000000052154</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22.36|15.16|5.22</t>
+          <t>40.0|33.33|16.67</t>
         </is>
       </c>
       <c r="K31" t="b">
@@ -2130,7 +2126,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RNWWW</t>
+          <t>SABA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2144,26 +2140,26 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.0080000003799796</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0080000003799796</v>
+        <v>8.170000076293945</v>
       </c>
       <c r="F32" t="n">
-        <v>0.003000000026077</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="G32" t="n">
-        <v>82200</v>
+        <v>73100</v>
       </c>
       <c r="H32" t="n">
-        <v>657.600031234324</v>
+        <v>593571.9916343689</v>
       </c>
       <c r="I32" t="n">
-        <v>0.006000000052154</v>
+        <v>8.170000076293945</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>40.0|33.33|16.67</t>
+          <t>1.72|0.97|0.86</t>
         </is>
       </c>
       <c r="K32" t="b">
@@ -2177,13 +2173,13 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SABA</t>
+          <t>SATL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2197,26 +2193,26 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8.119999885559082</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="E33" t="n">
-        <v>8.170000076293945</v>
+        <v>6.25</v>
       </c>
       <c r="F33" t="n">
-        <v>8.100000381469727</v>
+        <v>5.559999942779541</v>
       </c>
       <c r="G33" t="n">
-        <v>73100</v>
+        <v>14615200</v>
       </c>
       <c r="H33" t="n">
-        <v>593571.9916343689</v>
+        <v>86668133.49113464</v>
       </c>
       <c r="I33" t="n">
-        <v>8.170000076293945</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.72|0.97|0.86</t>
+          <t>48.18|15.73|8.58</t>
         </is>
       </c>
       <c r="K33" t="b">
@@ -2230,13 +2226,13 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SATL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2250,26 +2246,26 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5.929999828338623</v>
+        <v>70.93000030517578</v>
       </c>
       <c r="E34" t="n">
-        <v>6.25</v>
+        <v>72.62000274658203</v>
       </c>
       <c r="F34" t="n">
-        <v>5.559999942779541</v>
+        <v>70.54000091552734</v>
       </c>
       <c r="G34" t="n">
-        <v>14615200</v>
+        <v>2635300</v>
       </c>
       <c r="H34" t="n">
-        <v>86668133.49113464</v>
+        <v>186921829.8042298</v>
       </c>
       <c r="I34" t="n">
-        <v>3.380000114440918</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>48.18|15.73|8.58</t>
+          <t>9.57|6.72|5.64</t>
         </is>
       </c>
       <c r="K34" t="b">
@@ -2283,59 +2279,6 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>yahoo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>vcp</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>70.93000030517578</v>
-      </c>
-      <c r="E35" t="n">
-        <v>72.62000274658203</v>
-      </c>
-      <c r="F35" t="n">
-        <v>70.54000091552734</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2635300</v>
-      </c>
-      <c r="H35" t="n">
-        <v>186921829.8042298</v>
-      </c>
-      <c r="I35" t="n">
-        <v>71.15000152587891</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>9.57|6.72|5.64</t>
-        </is>
-      </c>
-      <c r="K35" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>4</v>
-      </c>
-      <c r="M35" t="n">
-        <v>260</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
         <v>3</v>
       </c>
     </row>
